--- a/LISTEN/Script/22_12/22_12.xlsx
+++ b/LISTEN/Script/22_12/22_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\LISTEN\Script\22_12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89271D7C-2E6A-4334-9002-8CAB540BDBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1D1E6A-E6F0-4701-B38F-7E9E933BEF1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17895" yWindow="10230" windowWidth="26130" windowHeight="9255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14820" yWindow="4275" windowWidth="23580" windowHeight="9255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1番" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="156">
   <si>
     <t>Fre</t>
   </si>
@@ -429,6 +429,218 @@
   </si>
   <si>
     <t>上着</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>企画書</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>きかくしょ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抑える</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>おさえる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抑制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>甘さ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>あまさ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>甜度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>おとな</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>はこ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>盒子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高級感</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>こうきゅうかん</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出す</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>だす</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拿出、营造</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>狙い</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ねらい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标、意图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>販売</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>はんばい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>価格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かかく</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>設定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>せってい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>〜だと</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>假定条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>店の棚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消費者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>しょうひしゃ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目に止まる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>めにとまる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>注意到</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目立つ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>めだつ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>显眼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>〜たりする</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>做……啦……啦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不完全列举</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>調整</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ちょうせい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指摘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>してき</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修正</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>しゅうせい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>今のように</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>就像现在这样</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>十分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>じゅうぶん</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>みせのたな</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -759,7 +971,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1305,6 +1517,286 @@
       </c>
       <c r="C44" s="2" t="s">
         <v>101</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A45" s="1">
+        <v>0</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A46" s="1">
+        <v>0</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A47" s="1">
+        <v>0</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A48" s="1">
+        <v>0</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A49" s="1">
+        <v>0</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A50" s="1">
+        <v>0</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A51" s="1">
+        <v>0</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A52" s="1">
+        <v>0</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A53" s="1">
+        <v>0</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A54" s="1">
+        <v>0</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A55" s="1">
+        <v>0</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A56" s="1">
+        <v>0</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A57" s="1">
+        <v>0</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A58" s="1">
+        <v>0</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A59" s="1">
+        <v>0</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A60" s="1">
+        <v>0</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A61" s="1">
+        <v>0</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A62" s="1">
+        <v>0</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A63" s="1">
+        <v>0</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A64" s="1">
+        <v>0</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A65" s="1">
+        <v>0</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A66" s="1">
+        <v>0</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A67" s="1">
+        <v>0</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/LISTEN/Script/22_12/22_12.xlsx
+++ b/LISTEN/Script/22_12/22_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\LISTEN\Script\22_12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1D1E6A-E6F0-4701-B38F-7E9E933BEF1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B6CBE6-DEDD-4ACC-B098-FDB975FEC1DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14820" yWindow="4275" windowWidth="23580" windowHeight="9255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/LISTEN/Script/22_12/22_12.xlsx
+++ b/LISTEN/Script/22_12/22_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\LISTEN\Script\22_12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B6CBE6-DEDD-4ACC-B098-FDB975FEC1DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46E3CEC-D4D5-48AB-B37E-48790D0462DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14820" yWindow="4275" windowWidth="23580" windowHeight="9255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="264">
   <si>
     <t>Fre</t>
   </si>
@@ -641,6 +641,437 @@
   </si>
   <si>
     <t>みせのたな</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>確か</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>たしか</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好像是…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金魚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>きんぎょ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飼ってる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かってる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"飼っている"的口语</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>汚れちゃう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>よごれちゃう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"汚れてしまう"口语</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>しなきゃならない</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>必须…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"しなければならない"口语</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>みず</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>螺贝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2ヶ月前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>にかげつまえ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>餌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>えさ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>饲料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>りょう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日当</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ひあ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日照；阳光照射</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>影響</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>えいきょう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>〜通りに</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>とおりに</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>按照…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄関</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>げんかん</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>〜ずに</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不…就…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>少ない</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>すくない</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>少</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>〜はいいとして</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>…暂且不论</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中山</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>なかやま</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新製品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>しんせいひん</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>せんたくき</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>洗濯機</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>つける</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>附着在…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>マニュアルの案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>说明书的草案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>詳細な</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>しょうさいな</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>取扱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>とりあつかい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作；使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>説明書</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>せつめいしょ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>簡単な</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かんたんな</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>簡易</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かんい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>印刷物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>いんさつぶつ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使い方</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>つかいかた</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>問題</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>もんだい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>もじ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>絵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>え</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>シンプル</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>简单；简洁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>簡潔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かんけつ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>简洁；简明；扼要</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>動画</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>どうが</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>视频；动画</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>洗剤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>せんざい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>洗涤剂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>あんな</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>那样的；那种的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余計な</t>
+  </si>
+  <si>
+    <t>よけいな</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多余的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>省く</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>はぶく</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>省略</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>字幕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>じまく</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>複数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ふくすう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多个</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>言語</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>げんご</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语言</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>対応</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>たいおう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ニーズ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -971,13 +1402,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="11.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.125" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1766,7 +2197,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
         <v>0</v>
       </c>
@@ -1777,7 +2208,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
         <v>0</v>
       </c>
@@ -1788,7 +2219,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
         <v>0</v>
       </c>
@@ -1797,6 +2228,550 @@
       </c>
       <c r="C67" s="2" t="s">
         <v>154</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A68" s="1">
+        <v>0</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A69" s="1">
+        <v>0</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A70" s="1">
+        <v>0</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A71" s="1">
+        <v>0</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A72" s="1">
+        <v>0</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A73" s="1">
+        <v>0</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A74" s="1">
+        <v>0</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A75" s="1">
+        <v>0</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A76" s="1">
+        <v>0</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A77" s="1">
+        <v>0</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A78" s="1">
+        <v>0</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A79" s="1">
+        <v>0</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A80" s="1">
+        <v>0</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A81" s="1">
+        <v>0</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A82" s="1">
+        <v>0</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A83" s="1">
+        <v>0</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A84" s="1">
+        <v>0</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A85" s="1">
+        <v>0</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A86" s="1">
+        <v>0</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A87" s="1">
+        <v>0</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A88" s="1">
+        <v>0</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A89" s="1">
+        <v>0</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A90" s="1">
+        <v>0</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A91" s="1">
+        <v>0</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A92" s="1">
+        <v>0</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A93" s="1">
+        <v>0</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A94" s="1">
+        <v>0</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A95" s="1">
+        <v>0</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A96" s="1">
+        <v>0</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A97" s="1">
+        <v>0</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A98" s="1">
+        <v>0</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A99" s="1">
+        <v>0</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A100" s="1">
+        <v>0</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A101" s="1">
+        <v>0</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A102" s="1">
+        <v>0</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A103" s="1">
+        <v>0</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A104" s="1">
+        <v>0</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A105" s="1">
+        <v>0</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A106" s="1">
+        <v>0</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A107" s="1">
+        <v>0</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A108" s="1">
+        <v>0</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A109" s="1">
+        <v>0</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A110" s="1">
+        <v>0</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A111" s="1">
+        <v>0</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>263</v>
       </c>
     </row>
   </sheetData>

--- a/LISTEN/Script/22_12/22_12.xlsx
+++ b/LISTEN/Script/22_12/22_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\LISTEN\Script\22_12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46E3CEC-D4D5-48AB-B37E-48790D0462DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D0E5FB-55FD-4E9B-8246-10994EDAE3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14820" yWindow="4275" windowWidth="23580" windowHeight="9255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="266">
   <si>
     <t>Fre</t>
   </si>
@@ -1072,6 +1072,14 @@
   </si>
   <si>
     <t>需求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>変更</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>へんこう</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1402,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D111"/>
+  <dimension ref="A1:D112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1955,10 +1963,10 @@
         <v>0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>103</v>
+        <v>264</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>104</v>
+        <v>265</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.15">
@@ -1966,13 +1974,10 @@
         <v>0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.15">
@@ -1980,13 +1985,13 @@
         <v>0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.15">
@@ -1994,10 +1999,13 @@
         <v>0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.15">
@@ -2005,13 +2013,10 @@
         <v>0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.15">
@@ -2019,10 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.15">
@@ -2030,13 +2038,10 @@
         <v>0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.15">
@@ -2044,13 +2049,13 @@
         <v>0</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.15">
@@ -2058,10 +2063,13 @@
         <v>0</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.15">
@@ -2069,10 +2077,10 @@
         <v>0</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.15">
@@ -2080,10 +2088,10 @@
         <v>0</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.15">
@@ -2091,10 +2099,10 @@
         <v>0</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.15">
@@ -2102,10 +2110,10 @@
         <v>0</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.15">
@@ -2113,10 +2121,10 @@
         <v>0</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.15">
@@ -2124,13 +2132,10 @@
         <v>0</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.15">
@@ -2138,13 +2143,13 @@
         <v>0</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.15">
@@ -2152,13 +2157,13 @@
         <v>0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.15">
@@ -2166,10 +2171,13 @@
         <v>0</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>127</v>
+        <v>142</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.15">
@@ -2177,10 +2185,10 @@
         <v>0</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.15">
@@ -2188,13 +2196,10 @@
         <v>0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.15">
@@ -2202,10 +2207,13 @@
         <v>0</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.15">
@@ -2213,10 +2221,10 @@
         <v>0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.15">
@@ -2224,10 +2232,10 @@
         <v>0</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.15">
@@ -2235,13 +2243,10 @@
         <v>0</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.15">
@@ -2249,10 +2254,13 @@
         <v>0</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.15">
@@ -2260,13 +2268,10 @@
         <v>0</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.15">
@@ -2274,13 +2279,13 @@
         <v>0</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.15">
@@ -2288,13 +2293,13 @@
         <v>0</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.15">
@@ -2302,10 +2307,13 @@
         <v>0</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.15">
@@ -2313,13 +2321,10 @@
         <v>0</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.15">
@@ -2327,10 +2332,13 @@
         <v>0</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.15">
@@ -2338,13 +2346,10 @@
         <v>0</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.15">
@@ -2352,13 +2357,13 @@
         <v>0</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.15">
@@ -2366,13 +2371,13 @@
         <v>0</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.15">
@@ -2380,10 +2385,13 @@
         <v>0</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.15">
@@ -2391,13 +2399,10 @@
         <v>0</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.15">
@@ -2405,10 +2410,13 @@
         <v>0</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.15">
@@ -2416,10 +2424,10 @@
         <v>0</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.15">
@@ -2427,13 +2435,10 @@
         <v>0</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.15">
@@ -2441,10 +2446,13 @@
         <v>0</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.15">
@@ -2452,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.15">
@@ -2463,10 +2471,10 @@
         <v>0</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.15">
@@ -2474,10 +2482,10 @@
         <v>0</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.15">
@@ -2485,10 +2493,10 @@
         <v>0</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.15">
@@ -2496,10 +2504,10 @@
         <v>0</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.15">
@@ -2507,10 +2515,10 @@
         <v>0</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.15">
@@ -2518,13 +2526,10 @@
         <v>0</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.15">
@@ -2532,10 +2537,13 @@
         <v>0</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.15">
@@ -2543,10 +2551,10 @@
         <v>0</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.15">
@@ -2554,10 +2562,10 @@
         <v>0</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.15">
@@ -2565,10 +2573,10 @@
         <v>0</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.15">
@@ -2576,10 +2584,10 @@
         <v>0</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.15">
@@ -2587,10 +2595,10 @@
         <v>0</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.15">
@@ -2598,10 +2606,10 @@
         <v>0</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.15">
@@ -2609,13 +2617,10 @@
         <v>0</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.15">
@@ -2623,10 +2628,13 @@
         <v>0</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.15">
@@ -2634,13 +2642,10 @@
         <v>0</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.15">
@@ -2648,13 +2653,13 @@
         <v>0</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.15">
@@ -2662,13 +2667,13 @@
         <v>0</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.15">
@@ -2676,10 +2681,13 @@
         <v>0</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.15">
@@ -2687,13 +2695,10 @@
         <v>0</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.15">
@@ -2701,13 +2706,13 @@
         <v>0</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.15">
@@ -2715,10 +2720,13 @@
         <v>0</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.15">
@@ -2726,13 +2734,10 @@
         <v>0</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.15">
@@ -2740,13 +2745,13 @@
         <v>0</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.15">
@@ -2754,13 +2759,13 @@
         <v>0</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.15">
@@ -2768,9 +2773,23 @@
         <v>0</v>
       </c>
       <c r="B111" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A112" s="1">
+        <v>0</v>
+      </c>
+      <c r="B112" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="C111" s="2" t="s">
+      <c r="C112" s="2" t="s">
         <v>263</v>
       </c>
     </row>

--- a/LISTEN/Script/22_12/22_12.xlsx
+++ b/LISTEN/Script/22_12/22_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\LISTEN\Script\22_12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D0E5FB-55FD-4E9B-8246-10994EDAE3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359E21C1-9FA8-4191-94F1-9608AC31DD50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14820" yWindow="4275" windowWidth="23580" windowHeight="9255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="265">
   <si>
     <t>Fre</t>
   </si>
@@ -929,10 +929,6 @@
   </si>
   <si>
     <t>文字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>もじ</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1963,10 +1959,10 @@
         <v>0</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.15">
@@ -2620,7 +2616,7 @@
         <v>227</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>228</v>
+        <v>24</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.15">
@@ -2628,13 +2624,13 @@
         <v>0</v>
       </c>
       <c r="B100" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C100" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="D100" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.15">
@@ -2642,10 +2638,10 @@
         <v>0</v>
       </c>
       <c r="B101" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.15">
@@ -2653,13 +2649,13 @@
         <v>0</v>
       </c>
       <c r="B102" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="D102" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.15">
@@ -2667,13 +2663,13 @@
         <v>0</v>
       </c>
       <c r="B103" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C103" s="2" t="s">
+      <c r="D103" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.15">
@@ -2681,13 +2677,13 @@
         <v>0</v>
       </c>
       <c r="B104" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="D104" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.15">
@@ -2695,10 +2691,10 @@
         <v>0</v>
       </c>
       <c r="B105" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C105" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.15">
@@ -2706,13 +2702,13 @@
         <v>0</v>
       </c>
       <c r="B106" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C106" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="D106" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.15">
@@ -2720,13 +2716,13 @@
         <v>0</v>
       </c>
       <c r="B107" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C107" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="D107" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.15">
@@ -2734,10 +2730,10 @@
         <v>0</v>
       </c>
       <c r="B108" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C108" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.15">
@@ -2745,13 +2741,13 @@
         <v>0</v>
       </c>
       <c r="B109" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="D109" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.15">
@@ -2759,13 +2755,13 @@
         <v>0</v>
       </c>
       <c r="B110" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="D110" s="2" t="s">
         <v>257</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.15">
@@ -2773,13 +2769,13 @@
         <v>0</v>
       </c>
       <c r="B111" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C111" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C111" s="2" t="s">
+      <c r="D111" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.15">
@@ -2787,10 +2783,10 @@
         <v>0</v>
       </c>
       <c r="B112" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C112" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>263</v>
       </c>
     </row>
   </sheetData>

--- a/LISTEN/Script/22_12/22_12.xlsx
+++ b/LISTEN/Script/22_12/22_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\LISTEN\Script\22_12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B6CBE6-DEDD-4ACC-B098-FDB975FEC1DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359E21C1-9FA8-4191-94F1-9608AC31DD50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14820" yWindow="4275" windowWidth="23580" windowHeight="9255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="265">
   <si>
     <t>Fre</t>
   </si>
@@ -641,6 +641,441 @@
   </si>
   <si>
     <t>みせのたな</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>確か</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>たしか</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好像是…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金魚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>きんぎょ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飼ってる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かってる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"飼っている"的口语</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>汚れちゃう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>よごれちゃう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"汚れてしまう"口语</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>しなきゃならない</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>必须…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"しなければならない"口语</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>みず</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>螺贝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2ヶ月前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>にかげつまえ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>餌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>えさ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>饲料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>りょう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日当</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ひあ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日照；阳光照射</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>影響</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>えいきょう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>〜通りに</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>とおりに</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>按照…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄関</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>げんかん</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>〜ずに</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不…就…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>少ない</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>すくない</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>少</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>〜はいいとして</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>…暂且不论</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中山</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>なかやま</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新製品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>しんせいひん</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>せんたくき</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>洗濯機</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>つける</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>附着在…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>マニュアルの案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>说明书的草案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>詳細な</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>しょうさいな</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>取扱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>とりあつかい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作；使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>説明書</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>せつめいしょ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>簡単な</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かんたんな</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>簡易</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かんい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>印刷物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>いんさつぶつ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使い方</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>つかいかた</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>問題</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>もんだい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>絵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>え</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>シンプル</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>简单；简洁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>簡潔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かんけつ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>简洁；简明；扼要</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>動画</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>どうが</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>视频；动画</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>洗剤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>せんざい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>洗涤剂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>あんな</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>那样的；那种的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余計な</t>
+  </si>
+  <si>
+    <t>よけいな</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多余的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>省く</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>はぶく</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>省略</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>字幕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>じまく</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>複数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ふくすう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多个</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>言語</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>げんご</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语言</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>対応</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>たいおう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ニーズ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>変更</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>へんこう</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -971,13 +1406,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="11.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.125" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1524,10 +1959,10 @@
         <v>0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>103</v>
+        <v>263</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>104</v>
+        <v>264</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.15">
@@ -1535,13 +1970,10 @@
         <v>0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.15">
@@ -1549,13 +1981,13 @@
         <v>0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.15">
@@ -1563,10 +1995,13 @@
         <v>0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.15">
@@ -1574,13 +2009,10 @@
         <v>0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.15">
@@ -1588,10 +2020,13 @@
         <v>0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.15">
@@ -1599,13 +2034,10 @@
         <v>0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.15">
@@ -1613,13 +2045,13 @@
         <v>0</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.15">
@@ -1627,10 +2059,13 @@
         <v>0</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.15">
@@ -1638,10 +2073,10 @@
         <v>0</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.15">
@@ -1649,10 +2084,10 @@
         <v>0</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.15">
@@ -1660,10 +2095,10 @@
         <v>0</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.15">
@@ -1671,10 +2106,10 @@
         <v>0</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.15">
@@ -1682,10 +2117,10 @@
         <v>0</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.15">
@@ -1693,13 +2128,10 @@
         <v>0</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.15">
@@ -1707,13 +2139,13 @@
         <v>0</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.15">
@@ -1721,13 +2153,13 @@
         <v>0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.15">
@@ -1735,10 +2167,13 @@
         <v>0</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>127</v>
+        <v>142</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.15">
@@ -1746,10 +2181,10 @@
         <v>0</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.15">
@@ -1757,46 +2192,601 @@
         <v>0</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A65" s="1">
+        <v>0</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C65" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D65" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A65" s="1">
-        <v>0</v>
-      </c>
-      <c r="B65" s="2" t="s">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A66" s="1">
+        <v>0</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C66" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A66" s="1">
-        <v>0</v>
-      </c>
-      <c r="B66" s="2" t="s">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A67" s="1">
+        <v>0</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C67" s="2" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A67" s="1">
-        <v>0</v>
-      </c>
-      <c r="B67" s="2" t="s">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A68" s="1">
+        <v>0</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C68" s="2" t="s">
         <v>154</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A69" s="1">
+        <v>0</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A70" s="1">
+        <v>0</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A71" s="1">
+        <v>0</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A72" s="1">
+        <v>0</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A73" s="1">
+        <v>0</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A74" s="1">
+        <v>0</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A75" s="1">
+        <v>0</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A76" s="1">
+        <v>0</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A77" s="1">
+        <v>0</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A78" s="1">
+        <v>0</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A79" s="1">
+        <v>0</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A80" s="1">
+        <v>0</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A81" s="1">
+        <v>0</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A82" s="1">
+        <v>0</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A83" s="1">
+        <v>0</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A84" s="1">
+        <v>0</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A85" s="1">
+        <v>0</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A86" s="1">
+        <v>0</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A87" s="1">
+        <v>0</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A88" s="1">
+        <v>0</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A89" s="1">
+        <v>0</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A90" s="1">
+        <v>0</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A91" s="1">
+        <v>0</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A92" s="1">
+        <v>0</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A93" s="1">
+        <v>0</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A94" s="1">
+        <v>0</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A95" s="1">
+        <v>0</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A96" s="1">
+        <v>0</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A97" s="1">
+        <v>0</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A98" s="1">
+        <v>0</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A99" s="1">
+        <v>0</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A100" s="1">
+        <v>0</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A101" s="1">
+        <v>0</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A102" s="1">
+        <v>0</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A103" s="1">
+        <v>0</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A104" s="1">
+        <v>0</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A105" s="1">
+        <v>0</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A106" s="1">
+        <v>0</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A107" s="1">
+        <v>0</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A108" s="1">
+        <v>0</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A109" s="1">
+        <v>0</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A110" s="1">
+        <v>0</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A111" s="1">
+        <v>0</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A112" s="1">
+        <v>0</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>

--- a/LISTEN/Script/22_12/22_12.xlsx
+++ b/LISTEN/Script/22_12/22_12.xlsx
@@ -461,171 +461,171 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>汚れちゃう</t>
+          <t>省く</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>よごれちゃう</t>
+          <t>はぶく</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>"汚れてしまう"口语</t>
+          <t>省略</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>影響</t>
+          <t>字幕</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>えいきょう</t>
+          <t>じまく</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>日当</t>
+          <t>複数</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ひあ</t>
+          <t>ふくすう</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>日照；阳光照射</t>
+          <t>多个</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>地域</t>
+          <t>集合</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ちいき</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>地区、社区</t>
-        </is>
-      </c>
+          <t>しゅうごう</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>確定</t>
+          <t>洗剤</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>かくてい</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>せんざい</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>洗涤剂</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>部長</t>
+          <t>修正</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ぶちょう</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>部长、社长</t>
-        </is>
-      </c>
+          <t>しゅうせい</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>留守番電話</t>
+          <t>迷惑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>るすばんでんわ</t>
+          <t>めいわく</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>电话答录机、语音信箱</t>
+          <t>麻烦；困扰；打扰</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>展覧会</t>
+          <t>到着</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>てんらんかい</t>
+          <t>とうちゃく</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ファイル</t>
+          <t>日当り</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>文件</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>ひあたり</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>日照；阳光照射</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -641,407 +641,427 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>タイトル</t>
+          <t>洗濯機</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>标题</t>
+          <t>せんたくき</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>文字</t>
+          <t>言語</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>もじ</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>げんご</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>语言</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>一回り</t>
+          <t>確認</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ひとまわり</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>一圈，一周</t>
-        </is>
-      </c>
+          <t>かくにん</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>位置</t>
+          <t>消費者</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>いち</t>
+          <t>しょうひしゃ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>いくらか</t>
+          <t>集合</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>少许、有点</t>
+          <t>しゅうごう</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>左に</t>
+          <t>余計な</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ひだりに</t>
+          <t>よけいな</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>みぎ-&gt;右边</t>
+          <t>多余的</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>日時</t>
+          <t>詳細な</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>にちじ</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
+          <t>しょうさいな</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>寄う</t>
+          <t>取扱</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>よそう</t>
+          <t>とりあつかい</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>聚集；集合</t>
+          <t>操作；使用</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>申し込む</t>
+          <t>説明書</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>もうしこむ</t>
+          <t>せつめいしょ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>下げる</t>
+          <t>一回り</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>さげる</t>
+          <t>ひとまわり</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>降低，降下</t>
+          <t>一圈，一周</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>上げる</t>
+          <t>当日</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>あげる</t>
+          <t>とうじつ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>玄関</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ていあん</t>
+          <t>げんかん</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>動かす</t>
+          <t>簡潔</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>うごかす</t>
+          <t>かんけつ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>移，移动</t>
+          <t>简洁；简明；扼要</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>出発</t>
+          <t>汚れちゃう</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>しゅっぱつ</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>よごれちゃう</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>"汚れてしまう"口语</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>集合</t>
+          <t>抑える</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>しゅうごう</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>おさえる</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>抑制</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>伝える</t>
+          <t>都合</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>つたえる</t>
+          <t>つごう</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>传达，转告</t>
+          <t>(某种)情况</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>合宿</t>
+          <t>調整</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>がっしゅく</t>
+          <t>ちょうせい</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>確認</t>
+          <t>日時</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>かくにん</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>にちじ</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>参加者</t>
+          <t>地域</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>さんかしゃ</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>ちいき</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>地区、社区</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>上着</t>
+          <t>狙い</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>うわぎ</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>ねらい</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>目标、意图</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>設定</t>
+          <t>対応</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>せってい</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>たいおう</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>对应</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>変更</t>
+          <t>使い方</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>へんこう</t>
+          <t>つかいかた</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>都合</t>
+          <t>動画</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>つごう</t>
+          <t>どうが</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>(某种)情况</t>
+          <t>视频；动画</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1061,227 +1081,235 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>当日</t>
+          <t>店の棚</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>とうじつ</t>
+          <t>みせのたな</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>集合</t>
+          <t>寄う</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>しゅうごう</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>よそう</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>聚集；集合</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>連絡</t>
+          <t>確定</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>れんらく</t>
+          <t>かくてい</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>到着</t>
+          <t>変更</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>とうちゃく</t>
+          <t>へんこう</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>変更</t>
+          <t>〜はいいとして</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>へんこう</t>
+          <t>…暂且不论</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>迷惑</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>めいわく</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>麻烦；困扰；打扰</t>
-        </is>
-      </c>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>朝晚</t>
+          <t>時期</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>あさばん</t>
+          <t>じき</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>早晨和晚上；早晚</t>
+          <t>时期；季节；时机</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>時期</t>
+          <t>販売</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>じき</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>时期；季节；时机</t>
-        </is>
-      </c>
+          <t>はんばい</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>気温</t>
+          <t>伝える</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>きおん</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>つたえる</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>传达，转告</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>低い</t>
+          <t>下げる</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ひくい</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>さげる</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>降低，降下</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>真ん中</t>
+          <t>人数</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>まんなか</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>正中，中间</t>
-        </is>
-      </c>
+          <t>にんずう</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>変更</t>
+          <t>餌</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>へんこう</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>えさ</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>饲料</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>企画書</t>
+          <t>左に</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>きかくしょ</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>ひだりに</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>みぎ-&gt;右边</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1289,109 +1317,97 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>抑える</t>
+          <t>設定</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>おさえる</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>抑制</t>
-        </is>
-      </c>
+          <t>せってい</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>甘さ</t>
+          <t>参加者</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>あまさ</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>甜度</t>
-        </is>
-      </c>
+          <t>さんかしゃ</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>大人</t>
+          <t>マニュアルの案</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>おとな</t>
+          <t>说明书的草案</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>箱</t>
+          <t>位置</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>はこ</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>盒子</t>
-        </is>
-      </c>
+          <t>いち</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>高級感</t>
+          <t>影響</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>こうきゅうかん</t>
+          <t>えいきょう</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>出す</t>
+          <t>動かす</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>だす</t>
+          <t>うごかす</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>拿出、营造</t>
+          <t>移，移动</t>
         </is>
       </c>
     </row>
@@ -1401,19 +1417,15 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>狙い</t>
+          <t>2ヶ月前</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ねらい</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>目标、意图</t>
-        </is>
-      </c>
+          <t>にかげつまえ</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1421,31 +1433,35 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>販売</t>
+          <t>シンプル</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>はんばい</t>
+          <t>简单；简洁</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>価格</t>
+          <t>〜たりする</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>かかく</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>做……啦……啦</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>不完全列举</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1453,107 +1469,103 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>人数</t>
+          <t>〜通りに</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>にんずう</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>とおりに</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>按照…</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>〜だと</t>
+          <t>合宿</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>假定条件</t>
+          <t>がっしゅく</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>生け花</t>
+          <t>文字</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>いけばな</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>插花</t>
-        </is>
-      </c>
+          <t>もじ</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>店の棚</t>
+          <t>生け花</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>みせのたな</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>いけばな</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>插花</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>少ない</t>
+          <t>金魚</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>すくない</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>少</t>
-        </is>
-      </c>
+          <t>きんぎょ</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>目に止まる</t>
+          <t>〜だと</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>めにとまる</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>注意到</t>
-        </is>
-      </c>
+          <t>假定条件</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1561,17 +1573,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>目立つ</t>
+          <t>絵</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>めだつ</t>
+          <t>え</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>显眼</t>
+          <t>图片</t>
         </is>
       </c>
     </row>
@@ -1581,17 +1593,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>〜たりする</t>
+          <t>しなきゃならない</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>做……啦……啦</t>
+          <t>必须…</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>不完全列举</t>
+          <t>"しなければならない"口语</t>
         </is>
       </c>
     </row>
@@ -1601,15 +1613,19 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>価格</t>
+          <t>飼ってる</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>かかく</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>かってる</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>"飼っている"的口语</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1617,15 +1633,19 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>調整</t>
+          <t>量</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ちょうせい</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>りょう</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>分量</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1633,32 +1653,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>指摘</t>
+          <t>中山</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>してき</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>指出</t>
-        </is>
-      </c>
+          <t>なかやま</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>修正</t>
+          <t>〜ずに</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>しゅうせい</t>
+          <t>不…就…</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -1669,15 +1685,19 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>今のように</t>
+          <t>確か</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>就像现在这样</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>たしか</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>好像是…</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1685,12 +1705,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>十分</t>
+          <t>あんな</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>じゅうぶん</t>
+          <t>那样的；那种的</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -1701,17 +1721,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>確か</t>
+          <t>指摘</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>たしか</t>
+          <t>してき</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>好像是…</t>
+          <t>指出</t>
         </is>
       </c>
     </row>
@@ -1721,28 +1741,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>金魚</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>きんぎょ</t>
+          <t>みず</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>〜はいいとして</t>
+          <t>価格</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>…暂且不论</t>
+          <t>かかく</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -1753,17 +1773,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>飼ってる</t>
+          <t>貝</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>かってる</t>
+          <t>かい</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>"飼っている"的口语</t>
+          <t>螺贝</t>
         </is>
       </c>
     </row>
@@ -1773,19 +1793,15 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>しなきゃならない</t>
+          <t>変更</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>必须…</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>"しなければならない"口语</t>
-        </is>
-      </c>
+          <t>へんこう</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1793,12 +1809,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>今のように</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>みず</t>
+          <t>就像现在这样</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -1809,19 +1825,15 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>貝</t>
+          <t>文字</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>かい</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>螺贝</t>
-        </is>
-      </c>
+          <t>もじ</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -1829,35 +1841,31 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2ヶ月前</t>
+          <t>十分</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>にかげつまえ</t>
+          <t>じゅうぶん</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>餌</t>
+          <t>出発</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>えさ</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>饲料</t>
-        </is>
-      </c>
+          <t>しゅっぱつ</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -1865,19 +1873,15 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>量</t>
+          <t>連絡</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>りょう</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>分量</t>
-        </is>
-      </c>
+          <t>れんらく</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -1885,32 +1889,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>〜通りに</t>
+          <t>簡易</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>とおりに</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>按照…</t>
-        </is>
-      </c>
+          <t>かんい</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>玄関</t>
+          <t>簡単な</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>げんかん</t>
+          <t>かんたんな</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -1921,12 +1921,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>〜ずに</t>
+          <t>問題</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>不…就…</t>
+          <t>もんだい</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>中山</t>
+          <t>印刷物</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>なかやま</t>
+          <t>いんさつぶつ</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -1953,53 +1953,49 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>絵</t>
+          <t>ファイル</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>え</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>图片</t>
-        </is>
-      </c>
+          <t>文件</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>消費者</t>
+          <t>新製品</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>しょうひしゃ</t>
+          <t>しんせいひん</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>対応</t>
+          <t>少ない</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>たいおう</t>
+          <t>すくない</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>对应</t>
+          <t>少</t>
         </is>
       </c>
     </row>
@@ -2009,15 +2005,19 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>洗濯機</t>
+          <t>目立つ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>せんたくき</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
+          <t>めだつ</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>显眼</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2025,83 +2025,91 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>つける</t>
+          <t>上げる</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>附着在…</t>
+          <t>あげる</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>マニュアルの案</t>
+          <t>留守番電話</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>说明书的草案</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
+          <t>るすばんでんわ</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>电话答录机、语音信箱</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>詳細な</t>
+          <t>気温</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>しょうさいな</t>
+          <t>きおん</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>取扱</t>
+          <t>甘さ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>とりあつかい</t>
+          <t>あまさ</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>操作；使用</t>
+          <t>甜度</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>説明書</t>
+          <t>朝晚</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>せつめいしょ</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>あさばん</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>早晨和晚上；早晚</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -2109,15 +2117,19 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>簡単な</t>
+          <t>部長</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>かんたんな</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
+          <t>ぶちょう</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>部长、社长</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -2125,12 +2137,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>簡易</t>
+          <t>申し込む</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>かんい</t>
+          <t>もうしこむ</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -2141,12 +2153,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>印刷物</t>
+          <t>展覧会</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>いんさつぶつ</t>
+          <t>てんらんかい</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -2157,12 +2169,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>使い方</t>
+          <t>いくらか</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>つかいかた</t>
+          <t>少许、有点</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -2173,15 +2185,19 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>問題</t>
+          <t>出す</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>もんだい</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
+          <t>だす</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>拿出、营造</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -2189,12 +2205,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>新製品</t>
+          <t>つける</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>しんせいひん</t>
+          <t>附着在…</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -2205,12 +2221,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>文字</t>
+          <t>低い</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>もじ</t>
+          <t>ひくい</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -2221,12 +2237,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>シンプル</t>
+          <t>上着</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>简单；简洁</t>
+          <t>うわぎ</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -2237,19 +2253,15 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>簡潔</t>
+          <t>価格</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>かんけつ</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>简洁；简明；扼要</t>
-        </is>
-      </c>
+          <t>かかく</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -2257,37 +2269,33 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>動画</t>
+          <t>変更</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>どうが</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>视频；动画</t>
-        </is>
-      </c>
+          <t>へんこう</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>洗剤</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>せんざい</t>
+          <t>はこ</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>洗涤剂</t>
+          <t>盒子</t>
         </is>
       </c>
     </row>
@@ -2297,109 +2305,101 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>あんな</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>那样的；那种的</t>
+          <t>ていあん</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>余計な</t>
+          <t>真ん中</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>よけいな</t>
+          <t>まんなか</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>多余的</t>
+          <t>正中，中间</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>省く</t>
+          <t>企画書</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>はぶく</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>省略</t>
-        </is>
-      </c>
+          <t>きかくしょ</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>字幕</t>
+          <t>大人</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>じまく</t>
+          <t>おとな</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>複数</t>
+          <t>高級感</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ふくすう</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>多个</t>
-        </is>
-      </c>
+          <t>こうきゅうかん</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>言語</t>
+          <t>目に止まる</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>げんご</t>
+          <t>めにとまる</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>语言</t>
+          <t>注意到</t>
         </is>
       </c>
     </row>

--- a/LISTEN/Script/22_12/22_12.xlsx
+++ b/LISTEN/Script/22_12/22_12.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\LISTEN\Script\22_12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359E21C1-9FA8-4191-94F1-9608AC31DD50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2673AEFF-7878-460A-A96F-FD8E30CB1114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14820" yWindow="4275" windowWidth="23580" windowHeight="9255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10560" yWindow="0" windowWidth="27840" windowHeight="20040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1番" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="4-5番" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="338">
   <si>
     <t>Fre</t>
   </si>
@@ -1076,6 +1076,298 @@
   </si>
   <si>
     <t>へんこう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卒業</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>そつぎょう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出張</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>しゅっちょう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出る</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>でる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出去，出来</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>断る</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ことわる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不应允，拒绝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>～ようがない</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法（做）…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文句をつける</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>もんくをつける</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>挑毛病、抱怨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受ける</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>うける</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>接受</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不満</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ふまん</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>優勝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ゆうしょう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冠军</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>相手</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>あいて</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对手</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>負ける</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>まける</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>落败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>に決まってる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>肯定会…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在口语中，ている 经常被缩略为 てる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海外</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かいがい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>国外</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>勤務</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>きんむ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不安</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ふあん</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参加</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>さんか</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>都合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>つごう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方便，状况</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遅刻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ちこく</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>連絡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>れんらく</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夕立</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ゆうだち</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>骤雨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>途中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>とちゅう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>続行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ぞっこう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>继续执行，继续进行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最後</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>さいご</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>過去</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かこ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抜く</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ぬく</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>超过</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>越える</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>こえる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>発送</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>はっそう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>作業</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>さぎょう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>昨年</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>さくねん</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>去年</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2798,9 +3090,399 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="16.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.875" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A3" s="1">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A4" s="1">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A5" s="1">
+        <v>0</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A6" s="1">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A7" s="1">
+        <v>0</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A8" s="1">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A9" s="1">
+        <v>0</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A10" s="1">
+        <v>0</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A11" s="1">
+        <v>0</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A12" s="1">
+        <v>0</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A13" s="1">
+        <v>0</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A14" s="1">
+        <v>0</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A15" s="1">
+        <v>0</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A16" s="1">
+        <v>0</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A17" s="1">
+        <v>0</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A18" s="1">
+        <v>0</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A19" s="1">
+        <v>0</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A20" s="1">
+        <v>0</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A21" s="1">
+        <v>0</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A22" s="1">
+        <v>0</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A23" s="1">
+        <v>0</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A24" s="1">
+        <v>0</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A25" s="1">
+        <v>0</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A26" s="1">
+        <v>0</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A27" s="1">
+        <v>0</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A28" s="1">
+        <v>0</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A29" s="1">
+        <v>0</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A30" s="1">
+        <v>0</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/LISTEN/Script/22_12/22_12.xlsx
+++ b/LISTEN/Script/22_12/22_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\LISTEN\Script\22_12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2673AEFF-7878-460A-A96F-FD8E30CB1114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC490BD-929B-407C-B32E-9E5A0AB3949B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10560" yWindow="0" windowWidth="27840" windowHeight="20040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7035" yWindow="480" windowWidth="27840" windowHeight="20040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1番" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="341">
   <si>
     <t>Fre</t>
   </si>
@@ -1368,6 +1368,18 @@
   </si>
   <si>
     <t>去年</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遅れる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>おくれる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>迟到</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3090,7 +3102,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -3482,10 +3494,24 @@
         <v>337</v>
       </c>
     </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A31" s="1">
+        <v>0</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/LISTEN/Script/22_12/22_12.xlsx
+++ b/LISTEN/Script/22_12/22_12.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\LISTEN\Script\22_12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC490BD-929B-407C-B32E-9E5A0AB3949B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359E21C1-9FA8-4191-94F1-9608AC31DD50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7035" yWindow="480" windowWidth="27840" windowHeight="20040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14820" yWindow="4275" windowWidth="23580" windowHeight="9255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1番" sheetId="1" r:id="rId1"/>
-    <sheet name="4-5番" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="265">
   <si>
     <t>Fre</t>
   </si>
@@ -1076,310 +1076,6 @@
   </si>
   <si>
     <t>へんこう</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>卒業</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>そつぎょう</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>出張</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>しゅっちょう</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>出る</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>でる</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>出去，出来</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>断る</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ことわる</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不应允，拒绝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>～ようがない</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无法（做）…</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>文句をつける</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>もんくをつける</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>挑毛病、抱怨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>受ける</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>うける</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>接受</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不満</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ふまん</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>優勝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ゆうしょう</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>冠军</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>相手</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>あいて</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对手</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>負ける</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>まける</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>落败</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>に決まってる</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>肯定会…</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在口语中，ている 经常被缩略为 てる</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>海外</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>かいがい</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>国外</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>勤務</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>きんむ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>工作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不安</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ふあん</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>参加</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>さんか</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>都合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>つごう</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>方便，状况</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>遅刻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ちこく</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>連絡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>れんらく</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>夕立</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ゆうだち</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>骤雨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>途中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>とちゅう</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>続行</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ぞっこう</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>继续执行，继续进行</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>最後</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>さいご</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>過去</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>かこ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>抜く</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ぬく</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>超过</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>越える</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>こえる</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>発送</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>はっそう</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>作業</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>さぎょう</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>昨年</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>さくねん</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>去年</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>遅れる</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>おくれる</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>迟到</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3102,416 +2798,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="16.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.875" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A3" s="1">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A4" s="1">
-        <v>0</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A5" s="1">
-        <v>0</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A6" s="1">
-        <v>0</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A7" s="1">
-        <v>0</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A8" s="1">
-        <v>0</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A9" s="1">
-        <v>0</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A10" s="1">
-        <v>0</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A11" s="1">
-        <v>0</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A12" s="1">
-        <v>0</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A13" s="1">
-        <v>0</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A14" s="1">
-        <v>0</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A15" s="1">
-        <v>0</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A16" s="1">
-        <v>0</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A17" s="1">
-        <v>0</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A18" s="1">
-        <v>0</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A19" s="1">
-        <v>0</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A20" s="1">
-        <v>0</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A21" s="1">
-        <v>0</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A22" s="1">
-        <v>0</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A23" s="1">
-        <v>0</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A24" s="1">
-        <v>0</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A25" s="1">
-        <v>0</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A26" s="1">
-        <v>0</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A27" s="1">
-        <v>0</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A28" s="1">
-        <v>0</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A29" s="1">
-        <v>0</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A30" s="1">
-        <v>0</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A31" s="1">
-        <v>0</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>340</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 

--- a/LISTEN/Script/22_12/22_12.xlsx
+++ b/LISTEN/Script/22_12/22_12.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\LISTEN\Script\22_12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC490BD-929B-407C-B32E-9E5A0AB3949B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700F3D74-3B64-4B23-B2CE-1EFE7B1454B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7035" yWindow="480" windowWidth="27840" windowHeight="20040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17520" yWindow="1005" windowWidth="20880" windowHeight="19995" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1番" sheetId="1" r:id="rId1"/>
-    <sheet name="4-5番" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="2番" sheetId="3" r:id="rId2"/>
+    <sheet name="3番" sheetId="4" r:id="rId3"/>
+    <sheet name="4-5番" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="356">
   <si>
     <t>Fre</t>
   </si>
@@ -1380,6 +1381,65 @@
   </si>
   <si>
     <t>迟到</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>会うの</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>见面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动词原形+「の」将动作名词化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卒業して以来だ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毕业以来的第一次</t>
+  </si>
+  <si>
+    <t>飛行機</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ひこうき</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>急がなくてもいいね</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不用捉急</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文句のつけようがなかった</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无可挑剔、没话说</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>信じる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>しんじる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>～でしょうがない</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>…得不得了</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1387,7 +1447,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1407,6 +1467,12 @@
       <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1433,7 +1499,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1442,6 +1508,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3101,8 +3170,28 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59F4CCE9-0ADE-455E-814A-3E796DF66193}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F59FFA0-155D-4471-9523-FF8DABB0354C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -3508,20 +3597,89 @@
         <v>340</v>
       </c>
     </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A32" s="1">
+        <v>0</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A33" s="1">
+        <v>0</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A34" s="1">
+        <v>0</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A35" s="1">
+        <v>0</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A36" s="1">
+        <v>0</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A37" s="1">
+        <v>0</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A38" s="1">
+        <v>0</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-</worksheet>
 </file>